--- a/h1_test_bispectrum_features.csv.xlsx
+++ b/h1_test_bispectrum_features.csv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project work\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61E9BB1E-C980-4AAA-9BD3-CA185AFAE978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CFD913D4-7D0D-45BA-A0D0-BEDD1517936B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1740" yWindow="1872" windowWidth="17280" windowHeight="8880" xr2:uid="{73EAC83A-8BF8-4454-BD90-6847741B9D75}"/>
   </bookViews>
